--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU01/HRM/post DFS_HRM-2031-0260/Panel 7/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU01/HRM/post DFS_HRM-2031-0260/Panel 7/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.70823</v>
+        <v>16.52197</v>
       </c>
       <c r="D2" t="n">
-        <v>16.64299</v>
+        <v>16.36015</v>
       </c>
       <c r="E2" t="n">
-        <v>16.76625</v>
+        <v>16.43381</v>
       </c>
       <c r="F2" t="n">
-        <v>42.3101</v>
+        <v>42.44798</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04944</v>
+        <v>0.0503</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8345</v>
+        <v>1.83526</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.70119</v>
+        <v>16.73748</v>
       </c>
       <c r="D3" t="n">
-        <v>16.42093</v>
+        <v>16.31146</v>
       </c>
       <c r="E3" t="n">
-        <v>16.6792</v>
+        <v>16.42022</v>
       </c>
       <c r="F3" t="n">
-        <v>42.58251</v>
+        <v>42.19057</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05122</v>
+        <v>0.04968</v>
       </c>
       <c r="H3" t="n">
-        <v>1.79978</v>
+        <v>1.82879</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.90108</v>
+        <v>16.88795</v>
       </c>
       <c r="D4" t="n">
-        <v>16.34704</v>
+        <v>16.48663</v>
       </c>
       <c r="E4" t="n">
-        <v>16.56513</v>
+        <v>16.59035</v>
       </c>
       <c r="F4" t="n">
-        <v>42.09952</v>
+        <v>42.50069</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05009</v>
+        <v>0.05059</v>
       </c>
       <c r="H4" t="n">
-        <v>1.79171</v>
+        <v>1.77648</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.61353</v>
+        <v>16.59209</v>
       </c>
       <c r="D6" t="n">
-        <v>16.10457</v>
+        <v>15.73791</v>
       </c>
       <c r="E6" t="n">
-        <v>16.6112</v>
+        <v>16.1435</v>
       </c>
       <c r="F6" t="n">
-        <v>21.33033</v>
+        <v>21.46297</v>
       </c>
       <c r="G6" t="n">
-        <v>33.78857</v>
+        <v>34.11802</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.57889</v>
+        <v>16.67428</v>
       </c>
       <c r="D7" t="n">
-        <v>16.12751</v>
+        <v>16.38132</v>
       </c>
       <c r="E7" t="n">
-        <v>16.53996</v>
+        <v>16.49496</v>
       </c>
       <c r="F7" t="n">
-        <v>21.61307</v>
+        <v>21.50654</v>
       </c>
       <c r="G7" t="n">
-        <v>34.00277</v>
+        <v>34.41617</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.58879</v>
+        <v>16.56054</v>
       </c>
       <c r="D8" t="n">
-        <v>16.16375</v>
+        <v>15.76239</v>
       </c>
       <c r="E8" t="n">
-        <v>16.44184</v>
+        <v>16.42792</v>
       </c>
       <c r="F8" t="n">
-        <v>21.93981</v>
+        <v>21.14541</v>
       </c>
       <c r="G8" t="n">
-        <v>33.7345</v>
+        <v>34.33704</v>
       </c>
     </row>
   </sheetData>
